--- a/reports/relatorio_revisao_pagamentos_agosto_2026_pendente.xlsx
+++ b/reports/relatorio_revisao_pagamentos_agosto_2026_pendente.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="83">
   <si>
     <t xml:space="preserve">RELATÓRIO DE REVISÃO DE PAGAMENTOS</t>
   </si>
@@ -61,7 +61,7 @@
     <t xml:space="preserve">Revisão manual: pagamento no principal</t>
   </si>
   <si>
-    <t xml:space="preserve">O pagamento foi lançado integralmente no principal. Confirmar se ele deveria ser juros do mês indicado antes de ajustar.</t>
+    <t xml:space="preserve">Recebido: R$ 350,00. Juros previstos: R$ 300,00. Diferença: R$ 50,00. O pagamento foi lançado integralmente no principal; confirmar se deveria ser juros.</t>
   </si>
   <si>
     <t xml:space="preserve">ANDRESSA OLIVEIRA ARAUJO</t>
@@ -70,6 +70,9 @@
     <t xml:space="preserve">07/07/2026</t>
   </si>
   <si>
+    <t xml:space="preserve">Recebido: R$ 3.900,00. Juros previstos: R$ 900,00. Diferença: R$ 3.000,00. O pagamento foi lançado integralmente no principal; confirmar se deveria ser juros.</t>
+  </si>
+  <si>
     <t xml:space="preserve">ISA PAULA MORAIS DOS ANJOS</t>
   </si>
   <si>
@@ -79,114 +82,183 @@
     <t xml:space="preserve">Revisão manual: pagamento dividido</t>
   </si>
   <si>
-    <t xml:space="preserve">O valor foi dividido entre juros e principal, mas o total não equivale ao juro mensal. Conferir antes de qualquer ajuste.</t>
+    <t xml:space="preserve">Recebido: R$ 280,00. Juros previstos: R$ 240,00. Diferença: R$ 40,00. O pagamento foi dividido entre juros e principal; conferir antes de ajustar.</t>
   </si>
   <si>
     <t xml:space="preserve">ARIANE FELIX DE LIMA SOUSA</t>
   </si>
   <si>
+    <t xml:space="preserve">Recebido: R$ 750,00. Juros previstos: R$ 750,00. Diferença: R$ 0,00. O pagamento foi lançado integralmente no principal; confirmar se deveria ser juros.</t>
+  </si>
+  <si>
     <t xml:space="preserve">LAURICE SILVA MASCARENHAS</t>
   </si>
   <si>
     <t xml:space="preserve">05/07/2026</t>
   </si>
   <si>
+    <t xml:space="preserve">Recebido: R$ 700,00. Juros previstos: R$ 500,00. Diferença: R$ 200,00. O pagamento foi lançado integralmente no principal; confirmar se deveria ser juros.</t>
+  </si>
+  <si>
     <t xml:space="preserve">ANDERSON SANTOS DE OLIVEIRA</t>
   </si>
   <si>
     <t xml:space="preserve">05/08/2026</t>
   </si>
   <si>
+    <t xml:space="preserve">Recebido: R$ 300,00. Juros previstos: R$ 300,00. Diferença: R$ 0,00. O pagamento foi lançado integralmente no principal; confirmar se deveria ser juros.</t>
+  </si>
+  <si>
     <t xml:space="preserve">RAIANA AURELINA NATIVIDADE DE JESUS DA SILVA</t>
   </si>
   <si>
+    <t xml:space="preserve">Recebido: R$ 960,00. Juros previstos: R$ 160,00. Diferença: R$ 800,00. O pagamento foi lançado integralmente no principal; confirmar se deveria ser juros.</t>
+  </si>
+  <si>
     <t xml:space="preserve">BRUNO CECILIO DE SOUZA</t>
   </si>
   <si>
+    <t xml:space="preserve">Recebido: R$ 1.000,00. Juros previstos: R$ 300,00. Diferença: R$ 700,00. O pagamento foi dividido entre juros e principal; conferir antes de ajustar.</t>
+  </si>
+  <si>
     <t xml:space="preserve">ALANA DO CARMO COSTA</t>
   </si>
   <si>
     <t xml:space="preserve">24/07/2026</t>
   </si>
   <si>
+    <t xml:space="preserve">Recebido: R$ 780,00. Juros previstos: R$ 180,00. Diferença: R$ 600,00. O pagamento foi dividido entre juros e principal; conferir antes de ajustar.</t>
+  </si>
+  <si>
     <t xml:space="preserve">MILA VANESSA GOMES LAGO</t>
   </si>
   <si>
     <t xml:space="preserve">08/08/2026</t>
   </si>
   <si>
+    <t xml:space="preserve">Recebido: R$ 347,62. Juros previstos: R$ 300,00. Diferença: R$ 47,62. O pagamento foi dividido entre juros e principal; conferir antes de ajustar.</t>
+  </si>
+  <si>
     <t xml:space="preserve">DAISY CONCEICAO SOUZA  NÃO EMPRESTAR</t>
   </si>
   <si>
     <t xml:space="preserve">06/08/2026</t>
   </si>
   <si>
+    <t xml:space="preserve">Recebido: R$ 1.000,00. Juros previstos: R$ 240,00. Diferença: R$ 760,00. O pagamento foi dividido entre juros e principal; conferir antes de ajustar.</t>
+  </si>
+  <si>
     <t xml:space="preserve">JAINE BONFIM GABRIEL</t>
   </si>
   <si>
+    <t xml:space="preserve">Recebido: R$ 800,00. Juros previstos: R$ 240,00. Diferença: R$ 560,00. O pagamento foi dividido entre juros e principal; conferir antes de ajustar.</t>
+  </si>
+  <si>
     <t xml:space="preserve">JOIR SENA BARBOSA</t>
   </si>
   <si>
     <t xml:space="preserve">28/07/2026</t>
   </si>
   <si>
+    <t xml:space="preserve">Recebido: R$ 400,00. Juros previstos: R$ 120,00. Diferença: R$ 280,00. O pagamento foi dividido entre juros e principal; conferir antes de ajustar.</t>
+  </si>
+  <si>
     <t xml:space="preserve">07/08/2026</t>
   </si>
   <si>
+    <t xml:space="preserve">Recebido: R$ 600,00. Juros previstos: R$ 180,00. Diferença: R$ 420,00. O pagamento foi dividido entre juros e principal; conferir antes de ajustar.</t>
+  </si>
+  <si>
     <t xml:space="preserve">EMILY CONCEIÇÃO DA SILVA</t>
   </si>
   <si>
+    <t xml:space="preserve">Recebido: R$ 1.330,00. Juros previstos: R$ 300,00. Diferença: R$ 1.030,00. O pagamento foi dividido entre juros e principal; conferir antes de ajustar.</t>
+  </si>
+  <si>
     <t xml:space="preserve">RAFAEL SANTOS DE JESUS</t>
   </si>
   <si>
     <t xml:space="preserve">04/08/2026</t>
   </si>
   <si>
+    <t xml:space="preserve">Recebido: R$ 459,44. Juros previstos: R$ 90,00. Diferença: R$ 369,44. O pagamento foi dividido entre juros e principal; conferir antes de ajustar.</t>
+  </si>
+  <si>
     <t xml:space="preserve">ANDREA FERREIRA DOS SANTOS</t>
   </si>
   <si>
     <t xml:space="preserve">10/08/2026</t>
   </si>
   <si>
+    <t xml:space="preserve">Recebido: R$ 910,00. Juros previstos: R$ 210,00. Diferença: R$ 700,00. O pagamento foi lançado integralmente no principal; confirmar se deveria ser juros.</t>
+  </si>
+  <si>
     <t xml:space="preserve">BRUNA VIEIRA DE OLIVEIRA</t>
   </si>
   <si>
     <t xml:space="preserve">13/07/2026</t>
   </si>
   <si>
+    <t xml:space="preserve">Recebido: R$ 390,00. Juros previstos: R$ 90,00. Diferença: R$ 300,00. O pagamento foi lançado integralmente no principal; confirmar se deveria ser juros.</t>
+  </si>
+  <si>
     <t xml:space="preserve">LUANA SILVA DOS SANTOS</t>
   </si>
   <si>
+    <t xml:space="preserve">Recebido: R$ 1.500,00. Juros previstos: R$ 300,00. Diferença: R$ 1.200,00. O pagamento foi dividido entre juros e principal; conferir antes de ajustar.</t>
+  </si>
+  <si>
     <t xml:space="preserve">JUNIOR  ADM - TATIANA DOS SANTOS</t>
   </si>
   <si>
     <t xml:space="preserve">13/08/2026</t>
   </si>
   <si>
+    <t xml:space="preserve">Recebido: R$ 1.100,00. Juros previstos: R$ 100,00. Diferença: R$ 1.000,00. O pagamento foi dividido entre juros e principal; conferir antes de ajustar.</t>
+  </si>
+  <si>
     <t xml:space="preserve">WILLIAM HENRIQUE DE JESUS CARNEIRO</t>
   </si>
   <si>
+    <t xml:space="preserve">Recebido: R$ 1.300,00. Juros previstos: R$ 300,00. Diferença: R$ 1.000,00. O pagamento foi dividido entre juros e principal; conferir antes de ajustar.</t>
+  </si>
+  <si>
     <t xml:space="preserve">JOAO VICENTE AGUIAR GUERRIERI</t>
   </si>
   <si>
     <t xml:space="preserve">17/07/2026</t>
   </si>
   <si>
+    <t xml:space="preserve">Recebido: R$ 160,65. Juros previstos: R$ 229,50. Diferença: R$ 68,85. O pagamento foi lançado integralmente no principal; confirmar se deveria ser juros.</t>
+  </si>
+  <si>
     <t xml:space="preserve">LUCIANO SANTOS ARAUJO</t>
   </si>
   <si>
     <t xml:space="preserve">09/08/2026</t>
   </si>
   <si>
+    <t xml:space="preserve">Recebido: R$ 213,83. Juros previstos: R$ 256,80. Diferença: R$ 42,97. O pagamento foi lançado integralmente no principal; confirmar se deveria ser juros.</t>
+  </si>
+  <si>
     <t xml:space="preserve">ISA VICTÓRIA ARAÚJO SANTOS</t>
   </si>
   <si>
+    <t xml:space="preserve">Recebido: R$ 222,92. Juros previstos: R$ 300,00. Diferença: R$ 77,08. O pagamento foi lançado integralmente no principal; confirmar se deveria ser juros.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recebido: R$ 156,05. Juros previstos: R$ 300,00. Diferença: R$ 143,95. O pagamento foi lançado integralmente no principal; confirmar se deveria ser juros.</t>
+  </si>
+  <si>
     <t xml:space="preserve">DAISY LUCIANA CARVALHO DO CARMO</t>
   </si>
   <si>
     <t xml:space="preserve">MARCOS SANTOS PEREIRA</t>
   </si>
   <si>
+    <t xml:space="preserve">Recebido: R$ 126,00. Juros previstos: R$ 180,00. Diferença: R$ 54,00. O pagamento foi lançado integralmente no principal; confirmar se deveria ser juros.</t>
+  </si>
+  <si>
     <t xml:space="preserve">IONALIA BRAZ DOS SANTOS</t>
   </si>
   <si>
@@ -196,7 +268,7 @@
     <t xml:space="preserve">Revisão manual: principal já zerado</t>
   </si>
   <si>
-    <t xml:space="preserve">O total recebido equivale ao juro mensal, mas não há principal disponível para estorno. Conferir manualmente.</t>
+    <t xml:space="preserve">Recebido: R$ 150,00. Juros previstos: R$ 150,00. O total equivale ao juro mensal, mas o principal já está zerado. Conferir manualmente.</t>
   </si>
 </sst>
 </file>
@@ -205,8 +277,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy\ hh:mm"/>
-    <numFmt numFmtId="166" formatCode="[$R$-pt-BR]\ #.##000"/>
+    <numFmt numFmtId="165" formatCode="[$-416]dd/mm/yyyy\ hh:mm"/>
+    <numFmt numFmtId="166" formatCode="[$-416]&quot;R$ &quot;#,##0.00"/>
     <numFmt numFmtId="167" formatCode="@"/>
   </numFmts>
   <fonts count="11">
@@ -668,7 +740,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="179.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="204.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="n">
         <v>46237.5513888889</v>
       </c>
@@ -691,7 +763,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="179.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="217.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="n">
         <v>46237.5715277778</v>
       </c>
@@ -711,15 +783,15 @@
         <v>12</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="166.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="191.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="n">
         <v>46237.7479166667</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>280</v>
@@ -728,21 +800,21 @@
         <v>240</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="179.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="191.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="n">
         <v>46237.7895833333</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>750</v>
@@ -757,15 +829,15 @@
         <v>12</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="179.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="204.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="n">
         <v>46238.5055555556</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C10" s="7" t="n">
         <v>700</v>
@@ -774,21 +846,21 @@
         <v>500</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>12</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="179.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="191.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="n">
         <v>46239.6965277778</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C11" s="12" t="n">
         <v>300</v>
@@ -797,21 +869,21 @@
         <v>300</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F11" s="14" t="s">
         <v>12</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="179.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="204.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="n">
         <v>46239.7034722222</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C12" s="7" t="n">
         <v>960</v>
@@ -820,21 +892,21 @@
         <v>160</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>12</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="166.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="204.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="n">
         <v>46240.6666666667</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C13" s="12" t="n">
         <v>1000</v>
@@ -843,21 +915,21 @@
         <v>300</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F13" s="16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="166.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="191.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="n">
         <v>46241.7069444444</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C14" s="7" t="n">
         <v>780</v>
@@ -866,21 +938,21 @@
         <v>180</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="166.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="191.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="n">
         <v>46242.4875</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C15" s="12" t="n">
         <v>347.62</v>
@@ -889,21 +961,21 @@
         <v>300</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="166.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="204.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="n">
         <v>46242.5604166667</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C16" s="7" t="n">
         <v>1000</v>
@@ -912,21 +984,21 @@
         <v>240</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="166.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="191.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="n">
         <v>46242.6034722222</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="C17" s="12" t="n">
         <v>800</v>
@@ -935,21 +1007,21 @@
         <v>240</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F17" s="16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="166.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="191.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="n">
         <v>46244.5506944444</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="C18" s="7" t="n">
         <v>400</v>
@@ -958,21 +1030,21 @@
         <v>120</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="F18" s="15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="166.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="191.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="n">
         <v>46244.5513888889</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="C19" s="12" t="n">
         <v>600</v>
@@ -981,21 +1053,21 @@
         <v>180</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="F19" s="16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="166.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="204.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="n">
         <v>46244.56875</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="C20" s="7" t="n">
         <v>1330</v>
@@ -1004,21 +1076,21 @@
         <v>300</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="166.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="191.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="10" t="n">
         <v>46244.8166666667</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="C21" s="12" t="n">
         <v>459.44</v>
@@ -1027,21 +1099,21 @@
         <v>90</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="F21" s="16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="179.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="204.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="n">
         <v>46244.8715277778</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="C22" s="7" t="n">
         <v>910</v>
@@ -1050,21 +1122,21 @@
         <v>210</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="F22" s="9" t="s">
         <v>12</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="179.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="204.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="10" t="n">
         <v>46246.7381944444</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="C23" s="12" t="n">
         <v>390</v>
@@ -1073,21 +1145,21 @@
         <v>90</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="F23" s="14" t="s">
         <v>12</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="166.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="204.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="n">
         <v>46247.4625</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="C24" s="7" t="n">
         <v>1500</v>
@@ -1096,21 +1168,21 @@
         <v>300</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="F24" s="15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="166.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="204.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="10" t="n">
         <v>46247.4979166667</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="C25" s="12" t="n">
         <v>1100</v>
@@ -1119,21 +1191,21 @@
         <v>100</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="F25" s="16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="166.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="204.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="n">
         <v>46247.7354166667</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="C26" s="7" t="n">
         <v>1300</v>
@@ -1142,21 +1214,21 @@
         <v>300</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="F26" s="15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="179.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="204.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="10" t="n">
         <v>46248.6840277778</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="C27" s="12" t="n">
         <v>160.65</v>
@@ -1165,21 +1237,21 @@
         <v>229.5</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="F27" s="14" t="s">
         <v>12</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="179.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="204.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="n">
         <v>46248.7715277778</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="C28" s="7" t="n">
         <v>213.83</v>
@@ -1188,21 +1260,21 @@
         <v>256.8</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="F28" s="9" t="s">
         <v>12</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="179.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="204.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="10" t="n">
         <v>46248.8180555556</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="C29" s="12" t="n">
         <v>222.92</v>
@@ -1211,21 +1283,21 @@
         <v>300</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F29" s="14" t="s">
         <v>12</v>
       </c>
       <c r="G29" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="179.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="204.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="n">
         <v>46248.81875</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="C30" s="7" t="n">
         <v>156.05</v>
@@ -1234,21 +1306,21 @@
         <v>300</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F30" s="9" t="s">
         <v>12</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="179.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="204.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="10" t="n">
         <v>46248.81875</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="C31" s="12" t="n">
         <v>156.05</v>
@@ -1257,21 +1329,21 @@
         <v>300</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F31" s="14" t="s">
         <v>12</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="166.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="204.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="n">
         <v>46249.5173611111</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="C32" s="7" t="n">
         <v>1300</v>
@@ -1280,21 +1352,21 @@
         <v>300</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="F32" s="15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="179.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="204.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="10" t="n">
         <v>46249.5506944444</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="C33" s="12" t="n">
         <v>126</v>
@@ -1303,21 +1375,21 @@
         <v>180</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="F33" s="14" t="s">
         <v>12</v>
       </c>
       <c r="G33" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="166.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="204.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="n">
         <v>46251.4868055556</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="C34" s="7" t="n">
         <v>150</v>
@@ -1326,13 +1398,13 @@
         <v>150</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
